--- a/content-sheets/campaign-content.xlsx
+++ b/content-sheets/campaign-content.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
   <si>
     <t>template</t>
   </si>
@@ -31,39 +31,15 @@
     <t>body_paragraph_2</t>
   </si>
   <si>
+    <t>eyebrow</t>
+  </si>
+  <si>
     <t>cta_url</t>
   </si>
   <si>
     <t>cta_text</t>
   </si>
   <si>
-    <t>footer_cta_url</t>
-  </si>
-  <si>
-    <t>unsubscribe_url</t>
-  </si>
-  <si>
-    <t>update_profile_url</t>
-  </si>
-  <si>
-    <t>data_notice_url</t>
-  </si>
-  <si>
-    <t>webview_url</t>
-  </si>
-  <si>
-    <t>services_url</t>
-  </si>
-  <si>
-    <t>contact_url</t>
-  </si>
-  <si>
-    <t>portal_url</t>
-  </si>
-  <si>
-    <t>eyebrow</t>
-  </si>
-  <si>
     <t>tip_label</t>
   </si>
   <si>
@@ -79,12 +55,6 @@
     <t>tip_link_text</t>
   </si>
   <si>
-    <t>note_label</t>
-  </si>
-  <si>
-    <t>note_body</t>
-  </si>
-  <si>
     <t>points_label</t>
   </si>
   <si>
@@ -112,30 +82,6 @@
     <t>aside_body</t>
   </si>
   <si>
-    <t>stat_1_value</t>
-  </si>
-  <si>
-    <t>stat_1_label</t>
-  </si>
-  <si>
-    <t>stat_2_value</t>
-  </si>
-  <si>
-    <t>stat_2_label</t>
-  </si>
-  <si>
-    <t>stat_3_value</t>
-  </si>
-  <si>
-    <t>stat_3_label</t>
-  </si>
-  <si>
-    <t>cta_headline</t>
-  </si>
-  <si>
-    <t>cta_body</t>
-  </si>
-  <si>
     <t>issue_date</t>
   </si>
   <si>
@@ -157,45 +103,30 @@
     <t>Filters should be checked monthly through the heavy-use months and changed at least every three months. We handle the inspection, the filters, the coils and the repairs — so nothing gets found the hard way on a 95° afternoon.</t>
   </si>
   <si>
+    <t>Peak Cooling Season</t>
+  </si>
+  <si>
     <t>https://www.safetyfacilityservices.com/request-a-quote</t>
   </si>
   <si>
     <t>Request a Quote</t>
   </si>
   <si>
-    <t>https://www.safetyfacilityservices.com/contact</t>
-  </si>
-  <si>
-    <t>#</t>
+    <t>Safety Tip</t>
+  </si>
+  <si>
+    <t>A Clean System Is a Cheaper System</t>
+  </si>
+  <si>
+    <t>Replacing a dirty filter with a clean one can cut a unit's energy use by 5 to 15 percent. Pair that with a lighting and energy review and both savings land on the same bill.</t>
   </si>
   <si>
     <t>https://www.safetyfacilityservices.com/services</t>
   </si>
   <si>
-    <t>https://www.safetyfacilityservices.com/customer-portal</t>
-  </si>
-  <si>
-    <t>Peak Cooling Season</t>
-  </si>
-  <si>
-    <t>Safety Tip</t>
-  </si>
-  <si>
-    <t>A Clean System Is a Cheaper System</t>
-  </si>
-  <si>
-    <t>Replacing a dirty filter with a clean one can cut a unit's energy use by 5 to 15 percent. Pair that with a lighting and energy review and both savings land on the same bill.</t>
-  </si>
-  <si>
     <t>Learn More</t>
   </si>
   <si>
-    <t>Good to know</t>
-  </si>
-  <si>
-    <t>Service cooling equipment in the spring and heating equipment in the fall — contractors book solid the week the weather turns.</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -217,9 +148,6 @@
     <t>Drift is a management problem, not a mop problem. Ours is built so that the standard is written down, someone is accountable for it by name, and it gets checked before you have to.</t>
   </si>
   <si>
-    <t>Schedule a Walkthrough</t>
-  </si>
-  <si>
     <t>Janitorial &amp; Cleaning</t>
   </si>
   <si>
@@ -250,30 +178,6 @@
     <t>Cleaning is a people business, and turnover is what breaks it. We hire selectively — only 5% of applicants are brought on — train through master trainers, and give every site a named account executive and client service manager rather than a queue.</t>
   </si>
   <si>
-    <t>CIMS-GB</t>
-  </si>
-  <si>
-    <t>Certified With Honors</t>
-  </si>
-  <si>
-    <t>98%+</t>
-  </si>
-  <si>
-    <t>Client Retention</t>
-  </si>
-  <si>
-    <t>30+ Yrs</t>
-  </si>
-  <si>
-    <t>All 50 States</t>
-  </si>
-  <si>
-    <t>Send us your current scope.</t>
-  </si>
-  <si>
-    <t>We'll walk the building, mark what the scope misses, and price the program against what your property actually needs.</t>
-  </si>
-  <si>
     <t>Pest Control</t>
   </si>
   <si>
@@ -296,12 +200,6 @@
   </si>
   <si>
     <t>Schedule a Site Inspection</t>
-  </si>
-  <si>
-    <t>Field note</t>
-  </si>
-  <si>
-    <t>Break down and remove cartons the day they land. Stacked cardboard in a back corridor is harborage, not storage — and it is the first thing an auditor photographs.</t>
   </si>
   <si>
     <t>Three entry points we always check</t>
@@ -706,13 +604,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AP4"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="42" width="34" customWidth="1"/>
+    <col min="1" max="24" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,443 +683,227 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="F2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="G2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="J2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="K2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="L2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="M2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="N2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="B3" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="C3" t="s">
         <v>41</v>
       </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" t="s">
+        <v>52</v>
+      </c>
+      <c r="V3" t="s">
+        <v>53</v>
+      </c>
+      <c r="W3" t="s">
+        <v>54</v>
+      </c>
+      <c r="X3" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N2" t="s">
-        <v>52</v>
-      </c>
-      <c r="O2" t="s">
-        <v>50</v>
-      </c>
-      <c r="P2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R2" t="s">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>55</v>
       </c>
-      <c r="S2" t="s">
+      <c r="B4" t="s">
         <v>56</v>
       </c>
-      <c r="T2" t="s">
+      <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="U2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="D4" t="s">
         <v>58</v>
       </c>
-      <c r="W2" t="s">
+      <c r="E4" t="s">
         <v>59</v>
       </c>
-      <c r="X2" t="s">
+      <c r="F4" t="s">
         <v>60</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
         <v>61</v>
       </c>
-      <c r="Z2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="I4" t="s">
         <v>62</v>
       </c>
-      <c r="B3" t="s">
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" t="s">
         <v>63</v>
       </c>
-      <c r="C3" t="s">
+      <c r="P4" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
+      <c r="Q4" t="s">
         <v>65</v>
       </c>
-      <c r="E3" t="s">
+      <c r="R4" t="s">
         <v>66</v>
       </c>
-      <c r="F3" t="s">
+      <c r="S4" t="s">
         <v>67</v>
       </c>
-      <c r="G3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="T4" t="s">
         <v>68</v>
       </c>
-      <c r="I3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3" t="s">
-        <v>52</v>
-      </c>
-      <c r="O3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="U4" t="s">
         <v>69</v>
       </c>
-      <c r="R3" t="s">
-        <v>61</v>
-      </c>
-      <c r="S3" t="s">
-        <v>61</v>
-      </c>
-      <c r="T3" t="s">
-        <v>61</v>
-      </c>
-      <c r="U3" t="s">
-        <v>61</v>
-      </c>
-      <c r="V3" t="s">
-        <v>61</v>
-      </c>
-      <c r="W3" t="s">
-        <v>61</v>
-      </c>
-      <c r="X3" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y3" t="s">
+      <c r="V4" t="s">
+        <v>38</v>
+      </c>
+      <c r="W4" t="s">
+        <v>38</v>
+      </c>
+      <c r="X4" t="s">
         <v>70</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I4" t="s">
-        <v>93</v>
-      </c>
-      <c r="J4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" t="s">
-        <v>51</v>
-      </c>
-      <c r="L4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" t="s">
-        <v>61</v>
-      </c>
-      <c r="O4" t="s">
-        <v>61</v>
-      </c>
-      <c r="P4" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>61</v>
-      </c>
-      <c r="R4" t="s">
-        <v>61</v>
-      </c>
-      <c r="S4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T4" t="s">
-        <v>61</v>
-      </c>
-      <c r="U4" t="s">
-        <v>61</v>
-      </c>
-      <c r="V4" t="s">
-        <v>61</v>
-      </c>
-      <c r="W4" t="s">
-        <v>95</v>
-      </c>
-      <c r="X4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/content-sheets/campaign-content.xlsx
+++ b/content-sheets/campaign-content.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="77">
   <si>
     <t>template</t>
   </si>
@@ -55,6 +55,12 @@
     <t>tip_link_text</t>
   </si>
   <si>
+    <t>note_label</t>
+  </si>
+  <si>
+    <t>note_body</t>
+  </si>
+  <si>
     <t>points_label</t>
   </si>
   <si>
@@ -127,6 +133,12 @@
     <t>Learn More</t>
   </si>
   <si>
+    <t>Good to know</t>
+  </si>
+  <si>
+    <t>Service cooling equipment in the spring and heating equipment in the fall — contractors book solid the week the weather turns.</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -200,6 +212,12 @@
   </si>
   <si>
     <t>Schedule a Site Inspection</t>
+  </si>
+  <si>
+    <t>Field note</t>
+  </si>
+  <si>
+    <t>Break down and remove cartons the day they land. Stacked cardboard in a back corridor is harborage, not storage — and it is the first thing an auditor photographs.</t>
   </si>
   <si>
     <t>Three entry points we always check</t>
@@ -604,13 +622,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="34" customWidth="1"/>
+    <col min="1" max="26" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,227 +701,251 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="U2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="V2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="W2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="X2" t="s">
-        <v>38</v>
+        <v>42</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="W3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="X3" t="s">
-        <v>38</v>
+        <v>57</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="P4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Q4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="R4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="S4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="T4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="V4" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="W4" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="X4" t="s">
-        <v>70</v>
+        <v>42</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
